--- a/results/job_matches_2026-09-07.xlsx
+++ b/results/job_matches_2026-09-07.xlsx
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Sqoop, HBase, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8dffe4f50c2f74c</t>
+          <t>https://www.indeed.com/viewjob?jk=83f3d0c20a7e71fe</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Cloud Network Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Ardor Digital Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,17 +521,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58b1135804a5c65d</t>
+          <t>https://www.indeed.com/viewjob?jk=a26a714c52ecd818</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-07.xlsx
+++ b/results/job_matches_2026-09-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,175 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Visibol</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AWS, SQS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d15bd8d2dcde66c</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer - Albany</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rocket Science Group</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a173f8b22852bf0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Cloud Network Engineer</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Ardor Digital Inc</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>San Jose, CA, US USA</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>10.4</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a26a714c52ecd818</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Semicon Service Nordic AB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Kafka, Oracle, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b82b7e5b56d16b4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Racine, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=001eb9aca1486771</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-07.xlsx
+++ b/results/job_matches_2026-09-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer - Albany</t>
+          <t>Cloud Solutions Architect 2 (Contractor) - 529701772</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rocket Science Group</t>
+          <t>RE/SPEC Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, NoSQL, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a173f8b22852bf0b</t>
+          <t>https://www.indeed.com/viewjob?jk=c458c043196a1c69</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ardor Digital Inc</t>
+          <t>Stream</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+          <t>AWS, IAM, RDS, GCP, BigQuery, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a26a714c52ecd818</t>
+          <t>https://www.indeed.com/viewjob?jk=3bddb4afe7c4caf5</t>
         </is>
       </c>
     </row>
@@ -613,20 +613,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Semicon Service Nordic AB</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Kafka, Oracle, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,147 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82b7e5b56d16b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=65dc6fa390e72ae6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Full-Stack Engineer - Albany</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rocket Science Group</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a173f8b22852bf0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Semicon Service Nordic AB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Kafka, Oracle, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b82b7e5b56d16b4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Racine, WI, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D9" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=001eb9aca1486771</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ardor Digital Inc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a26a714c52ecd818</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-07.xlsx
+++ b/results/job_matches_2026-09-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Databricks &amp; dbt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Semicon Service Nordic AB</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Kafka, Oracle, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b82b7e5b56d16b4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d233d87b66cf8ac</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer / Architect – Databricks &amp; dbt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Racine, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=001eb9aca1486771</t>
+          <t>https://www.indeed.com/viewjob?jk=8d01e7837ac03015</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Network Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ardor Digital Inc</t>
+          <t>Semicon Service Nordic AB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,15 +766,85 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, BigQuery, Kafka, Oracle, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b82b7e5b56d16b4c</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Racine, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=001eb9aca1486771</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cloud Network Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ardor Digital Inc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Kubernetes, CloudWatch</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a26a714c52ecd818</t>
         </is>
